--- a/data/feed_preview.xlsx
+++ b/data/feed_preview.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Общий фактор для всех; вес растёт, если у компании большой ФОТ или длинные контракты без индексации.</t>
+          <t>Рост цен влияет на себестоимость любой компании. Сильнее всего он затрагивает бизнес с большими расходами на персонал и с долгими контрактами без индексации.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Общий фактор для всех; вес растёт, если у компании большой ФОТ или длинные контракты без индексации.</t>
+          <t>Рост цен влияет на себестоимость любой компании. Сильнее всего он затрагивает бизнес с большими расходами на персонал и с долгими контрактами без индексации.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Общий фактор для всех; вес растёт, если у компании большой ФОТ или длинные контракты без индексации.</t>
+          <t>Рост цен влияет на себестоимость любой компании. Сильнее всего он затрагивает бизнес с большими расходами на персонал и с долгими контрактами без индексации.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Общий фактор для всех; вес растёт, если у компании большой ФОТ или длинные контракты без индексации.</t>
+          <t>Рост цен влияет на себестоимость любой компании. Сильнее всего он затрагивает бизнес с большими расходами на персонал и с долгими контрактами без индексации.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Производство/опт → снижение заказов бьёт по выручке и удлиняет оборачиваемость дебиторки.</t>
+          <t>Компания работает в производстве или оптовой торговле. Снижение заказов в промышленности может уменьшить выручку и увеличить срок оплаты от покупателей.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Производство/опт → снижение заказов бьёт по выручке и удлиняет оборачиваемость дебиторки.</t>
+          <t>Компания работает в производстве или оптовой торговле. Снижение заказов в промышленности может уменьшить выручку и увеличить срок оплаты от покупателей.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -929,8 +929,8 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Вес повышается, если страна ФТС упомянута в новости. Рекомендации — только проверка и комплаенс, без советов по обходу ограничений.
-ВЭД-компания → изменения пошлин напрямую меняют себестоимость.</t>
+          <t>Компания ведёт внешнеэкономическую деятельность, поэтому изменения санкционного режима могут затронуть её платежи, логистику и контрагентов. Стоит проверить, касаются ли меры конкретных стран, товаров и партнёров.
+Компания ведёт внешнеэкономическую деятельность. Изменение пошлин и таможенных правил прямо влияет на стоимость ввозимых товаров и сроки поставок.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Один поставщик ≥30% закупок → любой сбой в его отрасли критичен.</t>
+          <t>Больше 30% закупок компании приходится на одного поставщика. Любой сбой у него или в его отрасли может нарушить поставки.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1000,9 +1000,9 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Вес повышается, если страна ФТС упомянута в новости. Рекомендации — только проверка и комплаенс, без советов по обходу ограничений.
-ВЭД-компания → изменения пошлин напрямую меняют себестоимость.
-Один поставщик ≥30% закупок → любой сбой в его отрасли критичен.</t>
+          <t>Компания ведёт внешнеэкономическую деятельность, поэтому изменения санкционного режима могут затронуть её платежи, логистику и контрагентов. Стоит проверить, касаются ли меры конкретных стран, товаров и партнёров.
+Компания ведёт внешнеэкономическую деятельность. Изменение пошлин и таможенных правил прямо влияет на стоимость ввозимых товаров и сроки поставок.
+Больше 30% закупок компании приходится на одного поставщика. Любой сбой у него или в его отрасли может нарушить поставки.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Один поставщик ≥30% закупок → любой сбой в его отрасли критичен.</t>
+          <t>Больше 30% закупок компании приходится на одного поставщика. Любой сбой у него или в его отрасли может нарушить поставки.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Топливоёмкая отрасль → рост цен на дизель прямо в себестоимости.</t>
+          <t>В отрасли компании заметная доля затрат приходится на топливо. Изменения на рынке дизеля могут отразиться на расходах, но эффект нужно сверить с собственными затратами.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Есть гарантии → вероятна работа с госзаказом; уточнить в ответе как гипотезу, не факт.</t>
+          <t>У компании есть банковские гарантии, такие часто используются в госзакупках. Если компания работает с госзаказчиками, изменение бюджетных расходов может повлиять на её выручку.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
